--- a/retour-secu/ig/StructureDefinition-pdlgcReadme.xlsx
+++ b/retour-secu/ig/StructureDefinition-pdlgcReadme.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:17:43+00:00</t>
+    <t>2026-09-15T12:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
